--- a/conceptmaps-datatypes-part2/ig/CdaENPNToHumanNameConceptMap.xlsx
+++ b/conceptmaps-datatypes-part2/ig/CdaENPNToHumanNameConceptMap.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T09:46:03+00:00</t>
+    <t>2026-04-15T09:46:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/conceptmaps-datatypes-part2/ig/CdaENPNToHumanNameConceptMap.xlsx
+++ b/conceptmaps-datatypes-part2/ig/CdaENPNToHumanNameConceptMap.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T09:46:58+00:00</t>
+    <t>2026-04-15T09:49:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/conceptmaps-datatypes-part2/ig/CdaENPNToHumanNameConceptMap.xlsx
+++ b/conceptmaps-datatypes-part2/ig/CdaENPNToHumanNameConceptMap.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T09:49:42+00:00</t>
+    <t>2026-04-15T09:56:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/conceptmaps-datatypes-part2/ig/CdaENPNToHumanNameConceptMap.xlsx
+++ b/conceptmaps-datatypes-part2/ig/CdaENPNToHumanNameConceptMap.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T09:56:13+00:00</t>
+    <t>2026-04-20T09:24:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
